--- a/xls/lang/en.xlsx
+++ b/xls/lang/en.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="1196">
   <si>
     <t>情境</t>
   </si>
@@ -973,6 +973,39 @@
   </si>
   <si>
     <t>ui.guard-2</t>
+  </si>
+  <si>
+    <t>ui.rogue-1</t>
+  </si>
+  <si>
+    <t>ui.rogue-2</t>
+  </si>
+  <si>
+    <t>ui.orc</t>
+  </si>
+  <si>
+    <t>獸人</t>
+  </si>
+  <si>
+    <t>Orc</t>
+  </si>
+  <si>
+    <t>ui.wolf</t>
+  </si>
+  <si>
+    <t>狼</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>ui.horse</t>
+  </si>
+  <si>
+    <t>馬</t>
+  </si>
+  <si>
+    <t>Horse</t>
   </si>
   <si>
     <t>ui.ranger</t>
@@ -4039,7 +4072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F284"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5772,24 +5805,26 @@
         <v>318</v>
       </c>
       <c r="B117" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F117" s="4"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="4"/>
-    </row>
-    <row r="118" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="B118" s="4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
@@ -5799,27 +5834,29 @@
     </row>
     <row r="119" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
+      <c r="E119" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F119" s="4"/>
     </row>
-    <row r="120" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>323</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4" t="s">
@@ -5829,87 +5866,89 @@
     </row>
     <row r="121" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="D121" s="4"/>
+      <c r="E121" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F121" s="4"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="B122" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-    </row>
-    <row r="122" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B122" s="4" t="s">
+      <c r="C122" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="D122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
+    </row>
+    <row r="123" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F122" s="4"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="C123" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="D123" s="4"/>
+      <c r="E123" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F123" s="4"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="B124" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-    </row>
-    <row r="124" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B124" s="4" t="s">
+      <c r="C124" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="D124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
+    </row>
+    <row r="125" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F124" s="4"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="C125" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B125" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
+      <c r="E125" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F125" s="4"/>
     </row>
     <row r="126" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -5917,13 +5956,13 @@
     </row>
     <row r="127" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4" t="s">
@@ -5933,13 +5972,13 @@
     </row>
     <row r="128" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -5947,7 +5986,7 @@
     </row>
     <row r="129" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>347</v>
@@ -5972,30 +6011,26 @@
         <v>351</v>
       </c>
       <c r="D130" s="4"/>
-      <c r="E130" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E130" s="4"/>
       <c r="F130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B131" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
+    </row>
+    <row r="132" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D131" s="4"/>
-      <c r="E131" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F131" s="4"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>355</v>
@@ -6011,29 +6046,27 @@
     </row>
     <row r="133" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B133" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+    </row>
+    <row r="134" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="B134" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F133" s="4"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="3" t="s">
+      <c r="C134" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="s">
@@ -6043,13 +6076,13 @@
     </row>
     <row r="135" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B135" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C135" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4" t="s">
@@ -6059,13 +6092,13 @@
     </row>
     <row r="136" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
@@ -6075,13 +6108,13 @@
     </row>
     <row r="137" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B137" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4" t="s">
@@ -6091,13 +6124,13 @@
     </row>
     <row r="138" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4" t="s">
@@ -6107,13 +6140,13 @@
     </row>
     <row r="139" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B139" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4" t="s">
@@ -6123,13 +6156,13 @@
     </row>
     <row r="140" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="s">
@@ -6139,13 +6172,13 @@
     </row>
     <row r="141" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4" t="s">
@@ -6155,13 +6188,13 @@
     </row>
     <row r="142" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B142" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -6171,10 +6204,10 @@
     </row>
     <row r="143" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>382</v>
@@ -6187,7 +6220,7 @@
     </row>
     <row r="144" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>383</v>
@@ -6219,10 +6252,10 @@
     </row>
     <row r="146" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>389</v>
@@ -6235,13 +6268,13 @@
     </row>
     <row r="147" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="C147" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4" t="s">
@@ -6251,13 +6284,13 @@
     </row>
     <row r="148" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B148" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
@@ -6267,13 +6300,13 @@
     </row>
     <row r="149" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4" t="s">
@@ -6283,13 +6316,13 @@
     </row>
     <row r="150" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B150" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="s">
@@ -6299,13 +6332,13 @@
     </row>
     <row r="151" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4" t="s">
@@ -6315,13 +6348,13 @@
     </row>
     <row r="152" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B152" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="s">
@@ -6331,13 +6364,13 @@
     </row>
     <row r="153" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C153" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>407</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4" t="s">
@@ -6347,13 +6380,13 @@
     </row>
     <row r="154" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B154" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="s">
@@ -6363,13 +6396,13 @@
     </row>
     <row r="155" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4" t="s">
@@ -6379,13 +6412,13 @@
     </row>
     <row r="156" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B156" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="s">
@@ -6395,13 +6428,13 @@
     </row>
     <row r="157" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C157" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4" t="s">
@@ -6411,13 +6444,13 @@
     </row>
     <row r="158" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4" t="s">
@@ -6427,13 +6460,13 @@
     </row>
     <row r="159" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4" t="s">
@@ -6443,13 +6476,13 @@
     </row>
     <row r="160" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="s">
@@ -6459,13 +6492,13 @@
     </row>
     <row r="161" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4" t="s">
@@ -6475,13 +6508,13 @@
     </row>
     <row r="162" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="s">
@@ -6491,13 +6524,13 @@
     </row>
     <row r="163" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B163" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4" t="s">
@@ -6507,13 +6540,13 @@
     </row>
     <row r="164" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="s">
@@ -6523,13 +6556,13 @@
     </row>
     <row r="165" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4" t="s">
@@ -6539,13 +6572,13 @@
     </row>
     <row r="166" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4" t="s">
@@ -6555,13 +6588,13 @@
     </row>
     <row r="167" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>443</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4" t="s">
@@ -6571,13 +6604,13 @@
     </row>
     <row r="168" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="s">
@@ -6587,13 +6620,13 @@
     </row>
     <row r="169" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4" t="s">
@@ -6603,13 +6636,13 @@
     </row>
     <row r="170" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="s">
@@ -6619,13 +6652,13 @@
     </row>
     <row r="171" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>72</v>
+        <v>450</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4" t="s">
@@ -6633,15 +6666,15 @@
       </c>
       <c r="F171" s="4"/>
     </row>
-    <row r="172" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B172" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B172" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="C172" s="4" t="s">
-        <v>75</v>
+        <v>454</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4" t="s">
@@ -6665,15 +6698,15 @@
       </c>
       <c r="F173" s="4"/>
     </row>
-    <row r="174" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4" t="s">
@@ -6683,13 +6716,13 @@
     </row>
     <row r="175" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4" t="s">
@@ -6697,15 +6730,15 @@
       </c>
       <c r="F175" s="4"/>
     </row>
-    <row r="176" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>463</v>
+        <v>72</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4" t="s">
@@ -6713,15 +6746,15 @@
       </c>
       <c r="F176" s="4"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>466</v>
+        <v>74</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>467</v>
+        <v>75</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4" t="s">
@@ -6729,15 +6762,15 @@
       </c>
       <c r="F177" s="4"/>
     </row>
-    <row r="178" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B178" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4" t="s">
@@ -6745,15 +6778,15 @@
       </c>
       <c r="F178" s="4"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4" t="s">
@@ -6761,15 +6794,15 @@
       </c>
       <c r="F179" s="4"/>
     </row>
-    <row r="180" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B180" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C180" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>474</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
@@ -6777,15 +6810,15 @@
       </c>
       <c r="F180" s="4"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C181" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4" t="s">
@@ -6793,15 +6826,15 @@
       </c>
       <c r="F181" s="4"/>
     </row>
-    <row r="182" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B182" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>479</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4" t="s">
@@ -6809,15 +6842,15 @@
       </c>
       <c r="F182" s="4"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>467</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4" t="s">
@@ -6827,13 +6860,13 @@
     </row>
     <row r="184" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
@@ -6841,15 +6874,15 @@
       </c>
       <c r="F184" s="4"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4" t="s">
@@ -6859,13 +6892,13 @@
     </row>
     <row r="186" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4" t="s">
@@ -6873,15 +6906,15 @@
       </c>
       <c r="F186" s="4"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>486</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4" t="s">
@@ -6891,13 +6924,13 @@
     </row>
     <row r="188" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
@@ -6907,13 +6940,13 @@
     </row>
     <row r="189" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4" t="s">
@@ -6923,13 +6956,13 @@
     </row>
     <row r="190" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4" t="s">
@@ -6942,10 +6975,10 @@
         <v>494</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>391</v>
+        <v>495</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4" t="s">
@@ -6955,13 +6988,13 @@
     </row>
     <row r="192" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="s">
@@ -6971,13 +7004,13 @@
     </row>
     <row r="193" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4" t="s">
@@ -6987,13 +7020,13 @@
     </row>
     <row r="194" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4" t="s">
@@ -7003,13 +7036,13 @@
     </row>
     <row r="195" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4" t="s">
@@ -7019,13 +7052,13 @@
     </row>
     <row r="196" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>509</v>
+        <v>402</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4" t="s">
@@ -7033,15 +7066,15 @@
       </c>
       <c r="F196" s="4"/>
     </row>
-    <row r="197" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B197" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B197" s="4" t="s">
-        <v>511</v>
-      </c>
       <c r="C197" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="4" t="s">
@@ -7051,13 +7084,13 @@
     </row>
     <row r="198" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
@@ -7067,13 +7100,13 @@
     </row>
     <row r="199" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4" t="s">
@@ -7083,13 +7116,13 @@
     </row>
     <row r="200" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4" t="s">
@@ -7099,13 +7132,13 @@
     </row>
     <row r="201" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="4" t="s">
@@ -7113,15 +7146,15 @@
       </c>
       <c r="F201" s="4"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="4" t="s">
@@ -7131,13 +7164,13 @@
     </row>
     <row r="203" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4" t="s">
@@ -7147,13 +7180,13 @@
     </row>
     <row r="204" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4" t="s">
@@ -7163,13 +7196,13 @@
     </row>
     <row r="205" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4" t="s">
@@ -7179,13 +7212,13 @@
     </row>
     <row r="206" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="4" t="s">
@@ -7195,13 +7228,13 @@
     </row>
     <row r="207" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="4" t="s">
@@ -7211,13 +7244,13 @@
     </row>
     <row r="208" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4" t="s">
@@ -7227,13 +7260,13 @@
     </row>
     <row r="209" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B209" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="B209" s="4" t="s">
-        <v>545</v>
-      </c>
       <c r="C209" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4" t="s">
@@ -7243,13 +7276,13 @@
     </row>
     <row r="210" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="B210" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="4" t="s">
@@ -7259,13 +7292,13 @@
     </row>
     <row r="211" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>552</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4" t="s">
@@ -7275,13 +7308,13 @@
     </row>
     <row r="212" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="B212" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>555</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4" t="s">
@@ -7291,13 +7324,13 @@
     </row>
     <row r="213" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>557</v>
+        <v>528</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="4" t="s">
@@ -7307,13 +7340,13 @@
     </row>
     <row r="214" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="4" t="s">
@@ -7323,13 +7356,13 @@
     </row>
     <row r="215" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>158</v>
+        <v>560</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="4" t="s">
@@ -7339,13 +7372,13 @@
     </row>
     <row r="216" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="4" t="s">
@@ -7355,13 +7388,13 @@
     </row>
     <row r="217" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="4" t="s">
@@ -7371,13 +7404,13 @@
     </row>
     <row r="218" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="4" t="s">
@@ -7387,13 +7420,13 @@
     </row>
     <row r="219" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="4" t="s">
@@ -7403,13 +7436,13 @@
     </row>
     <row r="220" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="D220" s="4"/>
       <c r="E220" s="4" t="s">
@@ -7419,13 +7452,13 @@
     </row>
     <row r="221" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4" t="s">
@@ -7435,13 +7468,13 @@
     </row>
     <row r="222" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C222" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>582</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="4" t="s">
@@ -7451,13 +7484,13 @@
     </row>
     <row r="223" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C223" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4" t="s">
@@ -7467,13 +7500,13 @@
     </row>
     <row r="224" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B224" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="C224" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="4" t="s">
@@ -7489,7 +7522,7 @@
         <v>588</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>452</v>
+        <v>197</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4" t="s">
@@ -7505,7 +7538,7 @@
         <v>590</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4" t="s">
@@ -7515,10 +7548,10 @@
     </row>
     <row r="227" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B227" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>535</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>593</v>
@@ -7537,7 +7570,7 @@
         <v>595</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>596</v>
+        <v>457</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="4" t="s">
@@ -7547,69 +7580,77 @@
     </row>
     <row r="229" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B229" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="B229" s="4" t="s">
-        <v>598</v>
-      </c>
       <c r="C229" s="4" t="s">
-        <v>599</v>
+        <v>460</v>
       </c>
       <c r="D229" s="4"/>
-      <c r="E229" s="4"/>
+      <c r="E229" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F229" s="4"/>
     </row>
     <row r="230" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>602</v>
+        <v>463</v>
       </c>
       <c r="D230" s="4"/>
-      <c r="E230" s="4"/>
+      <c r="E230" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F230" s="4"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D231" s="4"/>
-      <c r="E231" s="4"/>
+      <c r="E231" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F231" s="4"/>
     </row>
     <row r="232" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>607</v>
+        <v>546</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D232" s="4"/>
-      <c r="E232" s="4"/>
+      <c r="E232" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F232" s="4"/>
     </row>
     <row r="233" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4" t="s">
@@ -7619,77 +7660,69 @@
     </row>
     <row r="234" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D234" s="4"/>
-      <c r="E234" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E234" s="4"/>
       <c r="F234" s="4"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D235" s="4"/>
-      <c r="E235" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E235" s="4"/>
       <c r="F235" s="4"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D236" s="4"/>
-      <c r="E236" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E236" s="4"/>
       <c r="F236" s="4"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D237" s="4"/>
-      <c r="E237" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E237" s="4"/>
       <c r="F237" s="4"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4" t="s">
@@ -7699,13 +7732,13 @@
     </row>
     <row r="239" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4" t="s">
@@ -7715,13 +7748,13 @@
     </row>
     <row r="240" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="4" t="s">
@@ -7731,13 +7764,13 @@
     </row>
     <row r="241" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="4" t="s">
@@ -7747,13 +7780,13 @@
     </row>
     <row r="242" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4" t="s">
@@ -7761,15 +7794,15 @@
       </c>
       <c r="F242" s="4"/>
     </row>
-    <row r="243" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4" t="s">
@@ -7779,13 +7812,13 @@
     </row>
     <row r="244" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4" t="s">
@@ -7795,13 +7828,13 @@
     </row>
     <row r="245" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4" t="s">
@@ -7811,13 +7844,13 @@
     </row>
     <row r="246" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="4" t="s">
@@ -7827,13 +7860,13 @@
     </row>
     <row r="247" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4" t="s">
@@ -7841,15 +7874,15 @@
       </c>
       <c r="F247" s="4"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="4" t="s">
@@ -7859,13 +7892,13 @@
     </row>
     <row r="249" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4" t="s">
@@ -7875,13 +7908,13 @@
     </row>
     <row r="250" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="4" t="s">
@@ -7891,13 +7924,13 @@
     </row>
     <row r="251" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4" t="s">
@@ -7907,13 +7940,13 @@
     </row>
     <row r="252" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="4" t="s">
@@ -7923,13 +7956,13 @@
     </row>
     <row r="253" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="4" t="s">
@@ -7939,13 +7972,13 @@
     </row>
     <row r="254" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D254" s="4"/>
       <c r="E254" s="4" t="s">
@@ -7955,13 +7988,13 @@
     </row>
     <row r="255" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4" t="s">
@@ -7971,13 +8004,13 @@
     </row>
     <row r="256" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="4" t="s">
@@ -7987,13 +8020,13 @@
     </row>
     <row r="257" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="4" t="s">
@@ -8003,13 +8036,13 @@
     </row>
     <row r="258" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="4" t="s">
@@ -8019,13 +8052,13 @@
     </row>
     <row r="259" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="4" t="s">
@@ -8035,13 +8068,13 @@
     </row>
     <row r="260" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D260" s="4"/>
       <c r="E260" s="4" t="s">
@@ -8051,13 +8084,13 @@
     </row>
     <row r="261" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="4" t="s">
@@ -8067,13 +8100,13 @@
     </row>
     <row r="262" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D262" s="4"/>
       <c r="E262" s="4" t="s">
@@ -8083,13 +8116,13 @@
     </row>
     <row r="263" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D263" s="4"/>
       <c r="E263" s="4" t="s">
@@ -8099,13 +8132,13 @@
     </row>
     <row r="264" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D264" s="4"/>
       <c r="E264" s="4" t="s">
@@ -8115,13 +8148,13 @@
     </row>
     <row r="265" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4" t="s">
@@ -8129,15 +8162,15 @@
       </c>
       <c r="F265" s="4"/>
     </row>
-    <row r="266" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D266" s="4"/>
       <c r="E266" s="4" t="s">
@@ -8145,15 +8178,15 @@
       </c>
       <c r="F266" s="4"/>
     </row>
-    <row r="267" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D267" s="4"/>
       <c r="E267" s="4" t="s">
@@ -8161,15 +8194,15 @@
       </c>
       <c r="F267" s="4"/>
     </row>
-    <row r="268" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4" t="s">
@@ -8177,15 +8210,15 @@
       </c>
       <c r="F268" s="4"/>
     </row>
-    <row r="269" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4" t="s">
@@ -8195,13 +8228,13 @@
     </row>
     <row r="270" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4" t="s">
@@ -8209,15 +8242,15 @@
       </c>
       <c r="F270" s="4"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4" t="s">
@@ -8225,15 +8258,15 @@
       </c>
       <c r="F271" s="4"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D272" s="4"/>
       <c r="E272" s="4" t="s">
@@ -8241,15 +8274,15 @@
       </c>
       <c r="F272" s="4"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4" t="s">
@@ -8257,15 +8290,15 @@
       </c>
       <c r="F273" s="4"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4" t="s">
@@ -8273,15 +8306,15 @@
       </c>
       <c r="F274" s="4"/>
     </row>
-    <row r="275" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4" t="s">
@@ -8289,15 +8322,15 @@
       </c>
       <c r="F275" s="4"/>
     </row>
-    <row r="276" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4" t="s">
@@ -8305,15 +8338,15 @@
       </c>
       <c r="F276" s="4"/>
     </row>
-    <row r="277" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D277" s="4"/>
       <c r="E277" s="4" t="s">
@@ -8323,13 +8356,13 @@
     </row>
     <row r="278" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4" t="s">
@@ -8338,20 +8371,100 @@
       <c r="F278" s="4"/>
     </row>
     <row r="279" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="5" t="s">
+      <c r="A279" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B279" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="D279" s="4"/>
+      <c r="E279" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F279" s="4"/>
+    </row>
+    <row r="280" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="B280" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="B279" s="6" t="s">
+      <c r="C280" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="C279" s="6" t="s">
+      <c r="D280" s="4"/>
+      <c r="E280" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F280" s="4"/>
+    </row>
+    <row r="281" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="D279" s="6"/>
-      <c r="E279" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F279" s="6"/>
+      <c r="B281" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D281" s="4"/>
+      <c r="E281" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F281" s="4"/>
+    </row>
+    <row r="282" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D282" s="4"/>
+      <c r="E282" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F282" s="4"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="B283" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="D283" s="4"/>
+      <c r="E283" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F283" s="4"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="D284" s="6"/>
+      <c r="E284" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F284" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8393,13 +8506,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
@@ -8409,13 +8522,13 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -8425,13 +8538,13 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
@@ -8441,13 +8554,13 @@
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
@@ -8457,7 +8570,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>239</v>
@@ -8471,13 +8584,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -8485,13 +8598,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -8501,7 +8614,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>242</v>
@@ -8515,7 +8628,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>245</v>
@@ -8529,7 +8642,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>248</v>
@@ -8543,7 +8656,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>251</v>
@@ -8557,7 +8670,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>254</v>
@@ -8571,7 +8684,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>257</v>
@@ -8587,7 +8700,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>30</v>
@@ -8601,13 +8714,13 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
@@ -8617,7 +8730,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>33</v>
@@ -8631,13 +8744,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
@@ -8647,7 +8760,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>36</v>
@@ -8661,7 +8774,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>39</v>
@@ -8675,13 +8788,13 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -8689,7 +8802,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>215</v>
@@ -8703,7 +8816,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>42</v>
@@ -8717,13 +8830,13 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
@@ -8733,7 +8846,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>264</v>
@@ -8747,13 +8860,13 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
@@ -8763,7 +8876,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>267</v>
@@ -8777,13 +8890,13 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
@@ -8793,13 +8906,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>794</v>
+        <v>805</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
@@ -8809,13 +8922,13 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
@@ -8825,13 +8938,13 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -8839,13 +8952,13 @@
     </row>
     <row r="32" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
@@ -8855,13 +8968,13 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -8869,13 +8982,13 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
@@ -8885,7 +8998,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>221</v>
@@ -8899,13 +9012,13 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
@@ -8915,7 +9028,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>224</v>
@@ -8929,7 +9042,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>227</v>
@@ -8943,13 +9056,13 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
@@ -8959,7 +9072,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>230</v>
@@ -8973,7 +9086,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>218</v>
@@ -8987,13 +9100,13 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -9001,27 +9114,27 @@
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
@@ -9031,27 +9144,27 @@
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -9059,27 +9172,27 @@
     </row>
     <row r="47" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -9087,13 +9200,13 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
@@ -9103,7 +9216,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>275</v>
@@ -9117,13 +9230,13 @@
     </row>
     <row r="51" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
@@ -9133,13 +9246,13 @@
     </row>
     <row r="52" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -9147,13 +9260,13 @@
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
@@ -9163,13 +9276,13 @@
     </row>
     <row r="54" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4" t="s">
@@ -9179,13 +9292,13 @@
     </row>
     <row r="55" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
@@ -9233,13 +9346,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -9247,13 +9360,13 @@
     </row>
     <row r="3" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -9263,13 +9376,13 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -9277,13 +9390,13 @@
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
@@ -9293,13 +9406,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -9307,13 +9420,13 @@
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
@@ -9323,13 +9436,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -9337,13 +9450,13 @@
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -9353,13 +9466,13 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -9367,13 +9480,13 @@
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
@@ -9383,13 +9496,13 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -9397,13 +9510,13 @@
     </row>
     <row r="13" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -9411,13 +9524,13 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -9425,13 +9538,13 @@
     </row>
     <row r="15" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -9439,13 +9552,13 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -9453,13 +9566,13 @@
     </row>
     <row r="17" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
@@ -9469,13 +9582,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -9483,13 +9596,13 @@
     </row>
     <row r="19" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -9497,13 +9610,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -9511,13 +9624,13 @@
     </row>
     <row r="21" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -9525,13 +9638,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -9539,13 +9652,13 @@
     </row>
     <row r="23" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -9553,13 +9666,13 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -9567,13 +9680,13 @@
     </row>
     <row r="25" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -9581,13 +9694,13 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -9595,13 +9708,13 @@
     </row>
     <row r="27" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -9609,13 +9722,13 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -9623,13 +9736,13 @@
     </row>
     <row r="29" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
@@ -9639,13 +9752,13 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -9653,13 +9766,13 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
@@ -9669,13 +9782,13 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -9683,13 +9796,13 @@
     </row>
     <row r="33" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -9697,13 +9810,13 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -9711,13 +9824,13 @@
     </row>
     <row r="35" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
@@ -9727,13 +9840,13 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -9741,13 +9854,13 @@
     </row>
     <row r="37" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
@@ -9757,13 +9870,13 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -9771,13 +9884,13 @@
     </row>
     <row r="39" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
@@ -9787,13 +9900,13 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -9801,13 +9914,13 @@
     </row>
     <row r="41" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4" t="s">
@@ -9817,13 +9930,13 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -9831,13 +9944,13 @@
     </row>
     <row r="43" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4" t="s">
@@ -9847,13 +9960,13 @@
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -9861,13 +9974,13 @@
     </row>
     <row r="45" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
@@ -9877,13 +9990,13 @@
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
@@ -9893,13 +10006,13 @@
     </row>
     <row r="47" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4" t="s">
@@ -9909,13 +10022,13 @@
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4" t="s">
@@ -9925,13 +10038,13 @@
     </row>
     <row r="49" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
@@ -9941,13 +10054,13 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
@@ -9957,13 +10070,13 @@
     </row>
     <row r="51" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>962</v>
+        <v>973</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
@@ -9973,13 +10086,13 @@
     </row>
     <row r="52" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -9987,13 +10100,13 @@
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
@@ -10003,13 +10116,13 @@
     </row>
     <row r="54" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -10017,13 +10130,13 @@
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4" t="s">
@@ -10033,13 +10146,13 @@
     </row>
     <row r="56" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -10047,13 +10160,13 @@
     </row>
     <row r="57" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4" t="s">
@@ -10063,13 +10176,13 @@
     </row>
     <row r="58" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -10077,13 +10190,13 @@
     </row>
     <row r="59" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>980</v>
+        <v>991</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4" t="s">
@@ -10093,13 +10206,13 @@
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -10107,13 +10220,13 @@
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4" t="s">
@@ -10123,13 +10236,13 @@
     </row>
     <row r="62" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -10137,13 +10250,13 @@
     </row>
     <row r="63" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4" t="s">
@@ -10153,13 +10266,13 @@
     </row>
     <row r="64" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -10167,13 +10280,13 @@
     </row>
     <row r="65" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
@@ -10221,13 +10334,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
@@ -10237,13 +10350,13 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -10253,7 +10366,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>96</v>
@@ -10269,13 +10382,13 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
@@ -10285,13 +10398,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
@@ -10301,13 +10414,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
@@ -10317,13 +10430,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -10333,13 +10446,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -10349,13 +10462,13 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
@@ -10365,13 +10478,13 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
@@ -10381,13 +10494,13 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
@@ -10397,13 +10510,13 @@
     </row>
     <row r="13" ht="110.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
@@ -10413,13 +10526,13 @@
     </row>
     <row r="14" ht="126" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
@@ -10429,13 +10542,13 @@
     </row>
     <row r="15" ht="126" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
@@ -10445,13 +10558,13 @@
     </row>
     <row r="16" ht="157.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
@@ -10461,13 +10574,13 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
@@ -10477,13 +10590,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
@@ -10493,13 +10606,13 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
@@ -10509,13 +10622,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
@@ -10525,13 +10638,13 @@
     </row>
     <row r="21" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
@@ -10541,13 +10654,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1045</v>
+        <v>1056</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
@@ -10595,13 +10708,13 @@
     </row>
     <row r="2" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
@@ -10611,13 +10724,13 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -10627,13 +10740,13 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
@@ -10643,13 +10756,13 @@
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
@@ -10659,13 +10772,13 @@
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
@@ -10675,13 +10788,13 @@
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
@@ -10691,13 +10804,13 @@
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -10707,13 +10820,13 @@
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -10723,13 +10836,13 @@
     </row>
     <row r="10" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
@@ -10739,13 +10852,13 @@
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
@@ -10755,13 +10868,13 @@
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
@@ -10771,13 +10884,13 @@
     </row>
     <row r="13" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
@@ -10787,13 +10900,13 @@
     </row>
     <row r="14" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
@@ -10803,13 +10916,13 @@
     </row>
     <row r="15" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
@@ -10819,13 +10932,13 @@
     </row>
     <row r="16" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1078</v>
+        <v>1089</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
@@ -10835,13 +10948,13 @@
     </row>
     <row r="17" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
@@ -10851,13 +10964,13 @@
     </row>
     <row r="18" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
@@ -10867,13 +10980,13 @@
     </row>
     <row r="19" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
@@ -10883,13 +10996,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
@@ -10899,13 +11012,13 @@
     </row>
     <row r="21" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
@@ -10915,13 +11028,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
@@ -10931,13 +11044,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
@@ -10947,13 +11060,13 @@
     </row>
     <row r="24" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
@@ -10963,13 +11076,13 @@
     </row>
     <row r="25" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
@@ -10979,13 +11092,13 @@
     </row>
     <row r="26" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
@@ -10995,13 +11108,13 @@
     </row>
     <row r="27" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4" t="s">
@@ -11011,13 +11124,13 @@
     </row>
     <row r="28" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
@@ -11027,13 +11140,13 @@
     </row>
     <row r="29" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
@@ -11043,13 +11156,13 @@
     </row>
     <row r="30" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
@@ -11059,13 +11172,13 @@
     </row>
     <row r="31" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
@@ -11075,13 +11188,13 @@
     </row>
     <row r="32" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
@@ -11091,13 +11204,13 @@
     </row>
     <row r="33" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
@@ -11107,13 +11220,13 @@
     </row>
     <row r="34" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
@@ -11123,13 +11236,13 @@
     </row>
     <row r="35" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
@@ -11139,13 +11252,13 @@
     </row>
     <row r="36" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
@@ -11155,13 +11268,13 @@
     </row>
     <row r="37" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
@@ -11171,13 +11284,13 @@
     </row>
     <row r="38" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4" t="s">
@@ -11187,13 +11300,13 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
@@ -11203,13 +11316,13 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1111</v>
+        <v>1122</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
@@ -11219,13 +11332,13 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4" t="s">
@@ -11235,13 +11348,13 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4" t="s">
@@ -11251,13 +11364,13 @@
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1116</v>
+        <v>1127</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>1117</v>
+        <v>1128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4" t="s">
@@ -11267,13 +11380,13 @@
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>1118</v>
+        <v>1129</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
@@ -11283,13 +11396,13 @@
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1121</v>
+        <v>1132</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
@@ -11299,13 +11412,13 @@
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1123</v>
+        <v>1134</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
@@ -11315,13 +11428,13 @@
     </row>
     <row r="47" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>1119</v>
+        <v>1130</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1124</v>
+        <v>1135</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1125</v>
+        <v>1136</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4" t="s">
@@ -11331,13 +11444,13 @@
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>1126</v>
+        <v>1137</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1127</v>
+        <v>1138</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1128</v>
+        <v>1139</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4" t="s">
@@ -11347,13 +11460,13 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
@@ -11363,13 +11476,13 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1132</v>
+        <v>1143</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
@@ -11379,13 +11492,13 @@
     </row>
     <row r="51" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
@@ -11395,13 +11508,13 @@
     </row>
     <row r="52" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4" t="s">
@@ -11411,13 +11524,13 @@
     </row>
     <row r="53" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
@@ -11427,13 +11540,13 @@
     </row>
     <row r="54" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4" t="s">
@@ -11443,13 +11556,13 @@
     </row>
     <row r="55" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4" t="s">
@@ -11459,13 +11572,13 @@
     </row>
     <row r="56" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4" t="s">
@@ -11475,13 +11588,13 @@
     </row>
     <row r="57" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4" t="s">
@@ -11491,13 +11604,13 @@
     </row>
     <row r="58" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4" t="s">
@@ -11507,13 +11620,13 @@
     </row>
     <row r="59" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4" t="s">
@@ -11523,13 +11636,13 @@
     </row>
     <row r="60" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4" t="s">
@@ -11539,13 +11652,13 @@
     </row>
     <row r="61" ht="78.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4" t="s">
@@ -11555,13 +11668,13 @@
     </row>
     <row r="62" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="s">
@@ -11571,13 +11684,13 @@
     </row>
     <row r="63" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1158</v>
+        <v>1169</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>1159</v>
+        <v>1170</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4" t="s">
@@ -11587,13 +11700,13 @@
     </row>
     <row r="64" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4" t="s">
@@ -11603,13 +11716,13 @@
     </row>
     <row r="65" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4" t="s">
@@ -11619,13 +11732,13 @@
     </row>
     <row r="66" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4" t="s">
@@ -11635,13 +11748,13 @@
     </row>
     <row r="67" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1166</v>
+        <v>1177</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>1167</v>
+        <v>1178</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4" t="s">
@@ -11651,13 +11764,13 @@
     </row>
     <row r="68" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>1169</v>
+        <v>1180</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4" t="s">
@@ -11667,13 +11780,13 @@
     </row>
     <row r="69" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>1172</v>
+        <v>1183</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4" t="s">
@@ -11683,13 +11796,13 @@
     </row>
     <row r="70" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>1174</v>
+        <v>1185</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4" t="s">
@@ -11699,13 +11812,13 @@
     </row>
     <row r="71" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1175</v>
+        <v>1186</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>1176</v>
+        <v>1187</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
@@ -11715,13 +11828,13 @@
     </row>
     <row r="72" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4" t="s">
@@ -11731,13 +11844,13 @@
     </row>
     <row r="73" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1164</v>
+        <v>1175</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
@@ -11747,13 +11860,13 @@
     </row>
     <row r="74" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>1177</v>
+        <v>1188</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>1178</v>
+        <v>1189</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
@@ -11769,7 +11882,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -11801,7 +11914,7 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>30</v>
@@ -11817,7 +11930,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>33</v>
@@ -11833,7 +11946,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>36</v>
@@ -11849,7 +11962,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>39</v>
@@ -11865,7 +11978,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>42</v>
@@ -11881,13 +11994,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
@@ -11897,13 +12010,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -11913,13 +12026,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>816</v>
+        <v>313</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1180</v>
+        <v>314</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -11929,13 +12042,13 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1049</v>
+        <v>827</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1050</v>
+        <v>1191</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
@@ -11945,13 +12058,13 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1051</v>
+        <v>1060</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
@@ -11961,13 +12074,13 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>1063</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>1064</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
@@ -11977,13 +12090,13 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
@@ -11992,20 +12105,36 @@
       <c r="F13" s="4"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="6"/>
+      <c r="A14" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12024,18 +12153,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>1181</v>
+        <v>1192</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1182</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>1183</v>
+        <v>1194</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1184</v>
+        <v>1195</v>
       </c>
     </row>
   </sheetData>

--- a/xls/lang/en.xlsx
+++ b/xls/lang/en.xlsx
@@ -6,18 +6,19 @@
   <sheets>
     <sheet sheetId="1" name="ui" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="item" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="ability" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="dialog" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="story" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="shared" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="meta" state="visible" r:id="rId10"/>
+    <sheet sheetId="3" name="role" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="ability" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="dialog" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="story" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="shared" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="meta" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1196">
   <si>
     <t>情境</t>
   </si>
@@ -828,124 +829,103 @@
     <t>Bottle</t>
   </si>
   <si>
-    <t>ui.wick</t>
-  </si>
-  <si>
-    <t>維克</t>
-  </si>
-  <si>
-    <t>Wick</t>
-  </si>
-  <si>
-    <t>冒險者</t>
-  </si>
-  <si>
-    <t>Adventurer</t>
-  </si>
-  <si>
-    <t>ui.dummy</t>
-  </si>
-  <si>
-    <t>木樁</t>
-  </si>
-  <si>
-    <t>Training Dummy</t>
-  </si>
-  <si>
-    <t>練習攻擊用</t>
-  </si>
-  <si>
-    <t>For combat practice</t>
-  </si>
-  <si>
-    <t>ui.musk</t>
-  </si>
-  <si>
-    <t>馬斯克</t>
-  </si>
-  <si>
-    <t>Musk</t>
-  </si>
-  <si>
-    <t>寡言卻可靠的中年壯漢，鍛造技術一流，據說曾是王都兵工坊的首席</t>
-  </si>
-  <si>
-    <t>A quiet but dependable man of middle years and a first-rate smith. Rumor has it he once ran the royal armory in the capital.</t>
-  </si>
-  <si>
-    <t>ui.trump</t>
-  </si>
-  <si>
-    <t>川普</t>
-  </si>
-  <si>
-    <t>Trump</t>
-  </si>
-  <si>
-    <t>胖胖和氣的大叔，愛講笑話和八卦，是村裡的情報中心。</t>
-  </si>
-  <si>
-    <t>A plump, good-natured fellow who loves jokes and gossip. If there's news in the village, he's heard it first.</t>
-  </si>
-  <si>
-    <t>ui.karen</t>
-  </si>
-  <si>
-    <t>凱倫</t>
-  </si>
-  <si>
-    <t>Gilly</t>
-  </si>
-  <si>
-    <t>每天從村外的田地或森林帶回最新鮮的農作物，推著小車叫賣，聲音又甜又響亮～</t>
-  </si>
-  <si>
-    <t>Every day she brings the freshest produce in from the fields and woods and hawks it from her cart, her voice sweet and loud~</t>
-  </si>
-  <si>
-    <t>ui.xi</t>
-  </si>
-  <si>
-    <t>習近平</t>
-  </si>
-  <si>
-    <t>Xi Jinping</t>
-  </si>
-  <si>
-    <t>負責村裡所有牲畜的宰殺與肉品加工。據說他手起刀落，比鐵匠還俐落……</t>
-  </si>
-  <si>
-    <t>Handles all the village's slaughtering and butchery. They say his cleaver comes down cleaner than the smith's hammer...</t>
-  </si>
-  <si>
-    <t>ui.macron</t>
-  </si>
-  <si>
-    <t>馬克宏</t>
-  </si>
-  <si>
-    <t>Macron</t>
-  </si>
-  <si>
-    <t>矮個子滿臉皺紋的小老頭，總能拿出些「你不知道自己需要的東西」。</t>
-  </si>
-  <si>
-    <t>A short, wrinkled old man who always seems to have "something you didn't know you needed."</t>
-  </si>
-  <si>
-    <t>ui.melanie</t>
-  </si>
-  <si>
-    <t>梅蘭妮</t>
-  </si>
-  <si>
-    <t>Melanie</t>
-  </si>
-  <si>
-    <t>漂亮大方的女士，跟川普共同經營一家旅館</t>
-  </si>
-  <si>
-    <t>A charming, generous lady who runs the inn with Trump.</t>
+    <t>ui.ranger</t>
+  </si>
+  <si>
+    <t>遊俠</t>
+  </si>
+  <si>
+    <t>Ranger</t>
+  </si>
+  <si>
+    <t>弓箭高手、森林獵人、野外生存達人，腳步輕盈如風，氣息比幽靈還難察覺</t>
+  </si>
+  <si>
+    <t>A master archer, forest hunter and wilderness survivor. Light-footed as the wind and harder to notice than a ghost.</t>
+  </si>
+  <si>
+    <t>ui.smith</t>
+  </si>
+  <si>
+    <t>鐵匠</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>打造武器、防具與工具的鍛造高手。</t>
+  </si>
+  <si>
+    <t>A skilled smith who forges weapons, armor and tools.</t>
+  </si>
+  <si>
+    <t>ui.innkeeper</t>
+  </si>
+  <si>
+    <t>旅館老闆</t>
+  </si>
+  <si>
+    <t>Innkeeper</t>
+  </si>
+  <si>
+    <t>經營旅館與酒館，消息靈通的熱情招待。</t>
+  </si>
+  <si>
+    <t>Runs the inn and tavern; a warm host who always knows the latest news.</t>
+  </si>
+  <si>
+    <t>ui.trader</t>
+  </si>
+  <si>
+    <t>小販</t>
+  </si>
+  <si>
+    <t>Trader</t>
+  </si>
+  <si>
+    <t>村內攤商，賣日用品或冒險裝備。</t>
+  </si>
+  <si>
+    <t>A village stallholder selling everyday goods and adventuring gear.</t>
+  </si>
+  <si>
+    <t>ui.butcher</t>
+  </si>
+  <si>
+    <t>解剖</t>
+  </si>
+  <si>
+    <t>Butcher</t>
+  </si>
+  <si>
+    <t>ui.merchant</t>
+  </si>
+  <si>
+    <t>行商</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>來去自如的商旅，販售異地貨品。</t>
+  </si>
+  <si>
+    <t>A traveling merchant selling goods from distant lands.</t>
+  </si>
+  <si>
+    <t>ui.guard</t>
+  </si>
+  <si>
+    <t>守衛</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>巡邏村莊、維持治安。</t>
+  </si>
+  <si>
+    <t>Patrols the village and keeps the peace.</t>
   </si>
   <si>
     <t>ui.rogue</t>
@@ -955,150 +935,6 @@
   </si>
   <si>
     <t>Bandit</t>
-  </si>
-  <si>
-    <t>ui.guard-1</t>
-  </si>
-  <si>
-    <t>守衛</t>
-  </si>
-  <si>
-    <t>Guard</t>
-  </si>
-  <si>
-    <t>駐守南門的守衛，跟搭檔輪流日夜巡邏村子</t>
-  </si>
-  <si>
-    <t>A guard posted at the south gate. Takes turns with a partner patrolling the village day and night.</t>
-  </si>
-  <si>
-    <t>ui.guard-2</t>
-  </si>
-  <si>
-    <t>ui.rogue-1</t>
-  </si>
-  <si>
-    <t>ui.rogue-2</t>
-  </si>
-  <si>
-    <t>ui.orc</t>
-  </si>
-  <si>
-    <t>獸人</t>
-  </si>
-  <si>
-    <t>Orc</t>
-  </si>
-  <si>
-    <t>ui.wolf</t>
-  </si>
-  <si>
-    <t>狼</t>
-  </si>
-  <si>
-    <t>Wolf</t>
-  </si>
-  <si>
-    <t>ui.horse</t>
-  </si>
-  <si>
-    <t>馬</t>
-  </si>
-  <si>
-    <t>Horse</t>
-  </si>
-  <si>
-    <t>ui.ranger</t>
-  </si>
-  <si>
-    <t>遊俠</t>
-  </si>
-  <si>
-    <t>Ranger</t>
-  </si>
-  <si>
-    <t>弓箭高手、森林獵人、野外生存達人，腳步輕盈如風，氣息比幽靈還難察覺</t>
-  </si>
-  <si>
-    <t>A master archer, forest hunter and wilderness survivor. Light-footed as the wind and harder to notice than a ghost.</t>
-  </si>
-  <si>
-    <t>ui.smith</t>
-  </si>
-  <si>
-    <t>鐵匠</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>打造武器、防具與工具的鍛造高手。</t>
-  </si>
-  <si>
-    <t>A skilled smith who forges weapons, armor and tools.</t>
-  </si>
-  <si>
-    <t>ui.innkeeper</t>
-  </si>
-  <si>
-    <t>旅館老闆</t>
-  </si>
-  <si>
-    <t>Innkeeper</t>
-  </si>
-  <si>
-    <t>經營旅館與酒館，消息靈通的熱情招待。</t>
-  </si>
-  <si>
-    <t>Runs the inn and tavern; a warm host who always knows the latest news.</t>
-  </si>
-  <si>
-    <t>ui.trader</t>
-  </si>
-  <si>
-    <t>小販</t>
-  </si>
-  <si>
-    <t>Trader</t>
-  </si>
-  <si>
-    <t>村內攤商，賣日用品或冒險裝備。</t>
-  </si>
-  <si>
-    <t>A village stallholder selling everyday goods and adventuring gear.</t>
-  </si>
-  <si>
-    <t>ui.butcher</t>
-  </si>
-  <si>
-    <t>解剖</t>
-  </si>
-  <si>
-    <t>Butcher</t>
-  </si>
-  <si>
-    <t>ui.merchant</t>
-  </si>
-  <si>
-    <t>行商</t>
-  </si>
-  <si>
-    <t>Merchant</t>
-  </si>
-  <si>
-    <t>來去自如的商旅，販售異地貨品。</t>
-  </si>
-  <si>
-    <t>A traveling merchant selling goods from distant lands.</t>
-  </si>
-  <si>
-    <t>ui.guard</t>
-  </si>
-  <si>
-    <t>巡邏村莊、維持治安。</t>
-  </si>
-  <si>
-    <t>Patrols the village and keeps the peace.</t>
   </si>
   <si>
     <t>ui.str</t>
@@ -2550,6 +2386,12 @@
     <t>item.dummy</t>
   </si>
   <si>
+    <t>木樁</t>
+  </si>
+  <si>
+    <t>Training Dummy</t>
+  </si>
+  <si>
     <t>練習攻擊用的木樁，可放置、可拿取</t>
   </si>
   <si>
@@ -2584,6 +2426,165 @@
   </si>
   <si>
     <t>A whole hide with the fur still on, skinned from an animal.</t>
+  </si>
+  <si>
+    <t>role.wick</t>
+  </si>
+  <si>
+    <t>維克</t>
+  </si>
+  <si>
+    <t>Wick</t>
+  </si>
+  <si>
+    <t>冒險者</t>
+  </si>
+  <si>
+    <t>Adventurer</t>
+  </si>
+  <si>
+    <t>role.trump</t>
+  </si>
+  <si>
+    <t>川普</t>
+  </si>
+  <si>
+    <t>Trump</t>
+  </si>
+  <si>
+    <t>胖胖和氣的大叔，愛講笑話和八卦，是村裡的情報中心。</t>
+  </si>
+  <si>
+    <t>A plump, good-natured fellow who loves jokes and gossip. If there's news in the village, he's heard it first.</t>
+  </si>
+  <si>
+    <t>role.melanie</t>
+  </si>
+  <si>
+    <t>梅蘭妮</t>
+  </si>
+  <si>
+    <t>Melanie</t>
+  </si>
+  <si>
+    <t>漂亮大方的女士，跟川普共同經營一家旅館</t>
+  </si>
+  <si>
+    <t>A charming, generous lady who runs the inn with Trump.</t>
+  </si>
+  <si>
+    <t>role.musk</t>
+  </si>
+  <si>
+    <t>馬斯克</t>
+  </si>
+  <si>
+    <t>Musk</t>
+  </si>
+  <si>
+    <t>寡言卻可靠的中年壯漢，鍛造技術一流，據說曾是王都兵工坊的首席</t>
+  </si>
+  <si>
+    <t>A quiet but dependable man of middle years and a first-rate smith. Rumor has it he once ran the royal armory in the capital.</t>
+  </si>
+  <si>
+    <t>role.karen</t>
+  </si>
+  <si>
+    <t>凱倫</t>
+  </si>
+  <si>
+    <t>Gilly</t>
+  </si>
+  <si>
+    <t>每天從村外的田地或森林帶回最新鮮的農作物，推著小車叫賣，聲音又甜又響亮～</t>
+  </si>
+  <si>
+    <t>Every day she brings the freshest produce in from the fields and woods and hawks it from her cart, her voice sweet and loud~</t>
+  </si>
+  <si>
+    <t>role.xi</t>
+  </si>
+  <si>
+    <t>習近平</t>
+  </si>
+  <si>
+    <t>Xi Jinping</t>
+  </si>
+  <si>
+    <t>負責村裡所有牲畜的宰殺與肉品加工。據說他手起刀落，比鐵匠還俐落……</t>
+  </si>
+  <si>
+    <t>Handles all the village's slaughtering and butchery. They say his cleaver comes down cleaner than the smith's hammer...</t>
+  </si>
+  <si>
+    <t>role.macron</t>
+  </si>
+  <si>
+    <t>馬克宏</t>
+  </si>
+  <si>
+    <t>Macron</t>
+  </si>
+  <si>
+    <t>矮個子滿臉皺紋的小老頭，總能拿出些「你不知道自己需要的東西」。</t>
+  </si>
+  <si>
+    <t>A short, wrinkled old man who always seems to have "something you didn't know you needed."</t>
+  </si>
+  <si>
+    <t>role.guard-1</t>
+  </si>
+  <si>
+    <t>駐守南門的守衛，跟搭檔輪流日夜巡邏村子</t>
+  </si>
+  <si>
+    <t>A guard posted at the south gate. Takes turns with a partner patrolling the village day and night.</t>
+  </si>
+  <si>
+    <t>role.guard-2</t>
+  </si>
+  <si>
+    <t>role.rogue-1</t>
+  </si>
+  <si>
+    <t>role.rogue-2</t>
+  </si>
+  <si>
+    <t>role.orc</t>
+  </si>
+  <si>
+    <t>獸人</t>
+  </si>
+  <si>
+    <t>Orc</t>
+  </si>
+  <si>
+    <t>role.wolf</t>
+  </si>
+  <si>
+    <t>狼</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>role.horse</t>
+  </si>
+  <si>
+    <t>馬</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>role.dummy</t>
+  </si>
+  <si>
+    <t>練習攻擊用</t>
+  </si>
+  <si>
+    <t>For combat practice</t>
   </si>
   <si>
     <t>ability.steal</t>
@@ -4072,7 +4073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F284"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5498,7 +5499,7 @@
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>269</v>
       </c>
@@ -5528,7 +5529,7 @@
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>274</v>
       </c>
@@ -5558,7 +5559,7 @@
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
     </row>
-    <row r="101" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>279</v>
       </c>
@@ -5588,7 +5589,7 @@
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
     </row>
-    <row r="103" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>284</v>
       </c>
@@ -5618,25 +5619,23 @@
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
     </row>
-    <row r="105" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F105" s="4"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>295</v>
@@ -5645,28 +5644,28 @@
         <v>296</v>
       </c>
       <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
+      <c r="E106" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F106" s="4"/>
     </row>
-    <row r="107" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F107" s="4"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>300</v>
@@ -5675,18 +5674,20 @@
         <v>301</v>
       </c>
       <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
+      <c r="E108" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F108" s="4"/>
     </row>
-    <row r="109" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4" t="s">
@@ -5696,27 +5697,29 @@
     </row>
     <row r="110" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F110" s="4"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C110" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-    </row>
-    <row r="111" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
-        <v>304</v>
-      </c>
       <c r="B111" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D111" s="4"/>
       <c r="E111" s="4" t="s">
@@ -5726,13 +5729,13 @@
     </row>
     <row r="112" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
@@ -5742,7 +5745,7 @@
     </row>
     <row r="113" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>313</v>
@@ -5751,18 +5754,20 @@
         <v>314</v>
       </c>
       <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F113" s="4"/>
     </row>
-    <row r="114" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4" t="s">
@@ -5772,27 +5777,29 @@
     </row>
     <row r="115" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
+      <c r="E115" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F115" s="4"/>
     </row>
-    <row r="116" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4" t="s">
@@ -5802,13 +5809,13 @@
     </row>
     <row r="117" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4" t="s">
@@ -5818,13 +5825,13 @@
     </row>
     <row r="118" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
@@ -5834,13 +5841,13 @@
     </row>
     <row r="119" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4" t="s">
@@ -5850,13 +5857,13 @@
     </row>
     <row r="120" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4" t="s">
@@ -5866,13 +5873,13 @@
     </row>
     <row r="121" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4" t="s">
@@ -5882,27 +5889,29 @@
     </row>
     <row r="122" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
+      <c r="E122" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F122" s="4"/>
     </row>
-    <row r="123" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4" t="s">
@@ -5912,27 +5921,29 @@
     </row>
     <row r="124" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
+      <c r="E124" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F124" s="4"/>
     </row>
-    <row r="125" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4" t="s">
@@ -5942,27 +5953,29 @@
     </row>
     <row r="126" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
+      <c r="E126" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F126" s="4"/>
     </row>
-    <row r="127" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4" t="s">
@@ -5972,27 +5985,29 @@
     </row>
     <row r="128" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
+      <c r="E128" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F128" s="4"/>
     </row>
-    <row r="129" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4" t="s">
@@ -6002,41 +6017,45 @@
     </row>
     <row r="130" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
+      <c r="E130" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D131" s="4"/>
-      <c r="E131" s="4"/>
+      <c r="E131" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F131" s="4"/>
     </row>
-    <row r="132" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4" t="s">
@@ -6046,27 +6065,29 @@
     </row>
     <row r="133" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
+      <c r="E133" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F133" s="4"/>
     </row>
-    <row r="134" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="s">
@@ -6076,13 +6097,13 @@
     </row>
     <row r="135" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4" t="s">
@@ -6092,13 +6113,13 @@
     </row>
     <row r="136" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
@@ -6108,13 +6129,13 @@
     </row>
     <row r="137" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4" t="s">
@@ -6124,13 +6145,13 @@
     </row>
     <row r="138" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4" t="s">
@@ -6140,13 +6161,13 @@
     </row>
     <row r="139" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4" t="s">
@@ -6156,13 +6177,13 @@
     </row>
     <row r="140" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="s">
@@ -6172,13 +6193,13 @@
     </row>
     <row r="141" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4" t="s">
@@ -6188,13 +6209,13 @@
     </row>
     <row r="142" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -6204,13 +6225,13 @@
     </row>
     <row r="143" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4" t="s">
@@ -6220,13 +6241,13 @@
     </row>
     <row r="144" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4" t="s">
@@ -6236,13 +6257,13 @@
     </row>
     <row r="145" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4" t="s">
@@ -6252,13 +6273,13 @@
     </row>
     <row r="146" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4" t="s">
@@ -6268,13 +6289,13 @@
     </row>
     <row r="147" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4" t="s">
@@ -6284,13 +6305,13 @@
     </row>
     <row r="148" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
@@ -6300,13 +6321,13 @@
     </row>
     <row r="149" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4" t="s">
@@ -6316,13 +6337,13 @@
     </row>
     <row r="150" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="s">
@@ -6332,13 +6353,13 @@
     </row>
     <row r="151" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>399</v>
+        <v>72</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4" t="s">
@@ -6346,15 +6367,15 @@
       </c>
       <c r="F151" s="4"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>402</v>
+        <v>74</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>403</v>
+        <v>75</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="s">
@@ -6364,13 +6385,13 @@
     </row>
     <row r="153" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4" t="s">
@@ -6378,15 +6399,15 @@
       </c>
       <c r="F153" s="4"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="s">
@@ -6396,13 +6417,13 @@
     </row>
     <row r="155" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4" t="s">
@@ -6410,15 +6431,15 @@
       </c>
       <c r="F155" s="4"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="s">
@@ -6428,13 +6449,13 @@
     </row>
     <row r="157" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4" t="s">
@@ -6442,15 +6463,15 @@
       </c>
       <c r="F157" s="4"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4" t="s">
@@ -6460,13 +6481,13 @@
     </row>
     <row r="159" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4" t="s">
@@ -6474,15 +6495,15 @@
       </c>
       <c r="F159" s="4"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="s">
@@ -6492,13 +6513,13 @@
     </row>
     <row r="161" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4" t="s">
@@ -6506,15 +6527,15 @@
       </c>
       <c r="F161" s="4"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="s">
@@ -6524,13 +6545,13 @@
     </row>
     <row r="163" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4" t="s">
@@ -6540,13 +6561,13 @@
     </row>
     <row r="164" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="s">
@@ -6556,13 +6577,13 @@
     </row>
     <row r="165" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4" t="s">
@@ -6572,13 +6593,13 @@
     </row>
     <row r="166" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4" t="s">
@@ -6588,13 +6609,13 @@
     </row>
     <row r="167" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4" t="s">
@@ -6604,10 +6625,10 @@
     </row>
     <row r="168" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>443</v>
@@ -6636,13 +6657,13 @@
     </row>
     <row r="170" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="s">
@@ -6652,10 +6673,10 @@
     </row>
     <row r="171" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>450</v>
+        <v>347</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>451</v>
@@ -6735,10 +6756,10 @@
         <v>464</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>72</v>
+        <v>465</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4" t="s">
@@ -6751,10 +6772,10 @@
         <v>464</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>74</v>
+        <v>467</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>75</v>
+        <v>468</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4" t="s">
@@ -6764,13 +6785,13 @@
     </row>
     <row r="178" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4" t="s">
@@ -6778,15 +6799,15 @@
       </c>
       <c r="F178" s="4"/>
     </row>
-    <row r="179" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4" t="s">
@@ -6796,13 +6817,13 @@
     </row>
     <row r="180" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
@@ -6810,15 +6831,15 @@
       </c>
       <c r="F180" s="4"/>
     </row>
-    <row r="181" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4" t="s">
@@ -6828,13 +6849,13 @@
     </row>
     <row r="182" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4" t="s">
@@ -6842,15 +6863,15 @@
       </c>
       <c r="F182" s="4"/>
     </row>
-    <row r="183" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4" t="s">
@@ -6860,13 +6881,13 @@
     </row>
     <row r="184" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
@@ -6874,15 +6895,15 @@
       </c>
       <c r="F184" s="4"/>
     </row>
-    <row r="185" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4" t="s">
@@ -6892,13 +6913,13 @@
     </row>
     <row r="186" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4" t="s">
@@ -6906,15 +6927,15 @@
       </c>
       <c r="F186" s="4"/>
     </row>
-    <row r="187" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4" t="s">
@@ -6924,13 +6945,13 @@
     </row>
     <row r="188" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
@@ -6940,13 +6961,13 @@
     </row>
     <row r="189" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4" t="s">
@@ -6956,13 +6977,13 @@
     </row>
     <row r="190" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4" t="s">
@@ -6972,13 +6993,13 @@
     </row>
     <row r="191" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4" t="s">
@@ -6988,13 +7009,13 @@
     </row>
     <row r="192" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="s">
@@ -7004,13 +7025,13 @@
     </row>
     <row r="193" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4" t="s">
@@ -7020,13 +7041,13 @@
     </row>
     <row r="194" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4" t="s">
@@ -7036,13 +7057,13 @@
     </row>
     <row r="195" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>504</v>
+        <v>158</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4" t="s">
@@ -7052,13 +7073,13 @@
     </row>
     <row r="196" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>402</v>
+        <v>521</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="4" t="s">
@@ -7068,13 +7089,13 @@
     </row>
     <row r="197" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="4" t="s">
@@ -7084,13 +7105,13 @@
     </row>
     <row r="198" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
@@ -7100,13 +7121,13 @@
     </row>
     <row r="199" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4" t="s">
@@ -7116,13 +7137,13 @@
     </row>
     <row r="200" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>518</v>
+        <v>197</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4" t="s">
@@ -7132,13 +7153,13 @@
     </row>
     <row r="201" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="4" t="s">
@@ -7146,15 +7167,15 @@
       </c>
       <c r="F201" s="4"/>
     </row>
-    <row r="202" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="4" t="s">
@@ -7164,13 +7185,13 @@
     </row>
     <row r="203" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>526</v>
+        <v>402</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4" t="s">
@@ -7180,13 +7201,13 @@
     </row>
     <row r="204" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>529</v>
+        <v>405</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4" t="s">
@@ -7196,13 +7217,13 @@
     </row>
     <row r="205" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>532</v>
+        <v>408</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4" t="s">
@@ -7212,13 +7233,13 @@
     </row>
     <row r="206" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="4" t="s">
@@ -7228,13 +7249,13 @@
     </row>
     <row r="207" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>537</v>
+        <v>491</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="4" t="s">
@@ -7244,13 +7265,13 @@
     </row>
     <row r="208" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4" t="s">
@@ -7260,77 +7281,69 @@
     </row>
     <row r="209" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D209" s="4"/>
-      <c r="E209" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E209" s="4"/>
       <c r="F209" s="4"/>
     </row>
     <row r="210" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="D210" s="4"/>
-      <c r="E210" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E210" s="4"/>
       <c r="F210" s="4"/>
     </row>
     <row r="211" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D211" s="4"/>
-      <c r="E211" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E211" s="4"/>
       <c r="F211" s="4"/>
     </row>
     <row r="212" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="D212" s="4"/>
-      <c r="E212" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="E212" s="4"/>
       <c r="F212" s="4"/>
     </row>
     <row r="213" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="4" t="s">
@@ -7340,13 +7353,13 @@
     </row>
     <row r="214" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="4" t="s">
@@ -7356,13 +7369,13 @@
     </row>
     <row r="215" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="4" t="s">
@@ -7372,13 +7385,13 @@
     </row>
     <row r="216" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="4" t="s">
@@ -7388,13 +7401,13 @@
     </row>
     <row r="217" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="4" t="s">
@@ -7404,13 +7417,13 @@
     </row>
     <row r="218" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="4" t="s">
@@ -7420,13 +7433,13 @@
     </row>
     <row r="219" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="4" t="s">
@@ -7436,13 +7449,13 @@
     </row>
     <row r="220" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>158</v>
+        <v>588</v>
       </c>
       <c r="D220" s="4"/>
       <c r="E220" s="4" t="s">
@@ -7452,13 +7465,13 @@
     </row>
     <row r="221" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="4" t="s">
@@ -7468,13 +7481,13 @@
     </row>
     <row r="222" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="4" t="s">
@@ -7482,15 +7495,15 @@
       </c>
       <c r="F222" s="4"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="4" t="s">
@@ -7500,13 +7513,13 @@
     </row>
     <row r="224" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="4" t="s">
@@ -7516,13 +7529,13 @@
     </row>
     <row r="225" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>197</v>
+        <v>603</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4" t="s">
@@ -7532,13 +7545,13 @@
     </row>
     <row r="226" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4" t="s">
@@ -7548,13 +7561,13 @@
     </row>
     <row r="227" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="4" t="s">
@@ -7564,13 +7577,13 @@
     </row>
     <row r="228" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>457</v>
+        <v>612</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="4" t="s">
@@ -7580,13 +7593,13 @@
     </row>
     <row r="229" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>460</v>
+        <v>615</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4" t="s">
@@ -7596,13 +7609,13 @@
     </row>
     <row r="230" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>463</v>
+        <v>618</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="4" t="s">
@@ -7612,13 +7625,13 @@
     </row>
     <row r="231" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="4" t="s">
@@ -7628,13 +7641,13 @@
     </row>
     <row r="232" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>546</v>
+        <v>623</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="4" t="s">
@@ -7644,13 +7657,13 @@
     </row>
     <row r="233" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4" t="s">
@@ -7660,69 +7673,77 @@
     </row>
     <row r="234" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
+      <c r="E234" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F234" s="4"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
+      <c r="E235" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F235" s="4"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="D236" s="4"/>
-      <c r="E236" s="4"/>
+      <c r="E236" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F236" s="4"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="D237" s="4"/>
-      <c r="E237" s="4"/>
+      <c r="E237" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F237" s="4"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4" t="s">
@@ -7732,13 +7753,13 @@
     </row>
     <row r="239" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4" t="s">
@@ -7748,13 +7769,13 @@
     </row>
     <row r="240" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="4" t="s">
@@ -7764,13 +7785,13 @@
     </row>
     <row r="241" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="4" t="s">
@@ -7780,13 +7801,13 @@
     </row>
     <row r="242" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4" t="s">
@@ -7796,13 +7817,13 @@
     </row>
     <row r="243" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4" t="s">
@@ -7812,13 +7833,13 @@
     </row>
     <row r="244" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4" t="s">
@@ -7828,13 +7849,13 @@
     </row>
     <row r="245" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4" t="s">
@@ -7842,15 +7863,15 @@
       </c>
       <c r="F245" s="4"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="4" t="s">
@@ -7858,15 +7879,15 @@
       </c>
       <c r="F246" s="4"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="4" t="s">
@@ -7876,13 +7897,13 @@
     </row>
     <row r="248" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="4" t="s">
@@ -7890,15 +7911,15 @@
       </c>
       <c r="F248" s="4"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4" t="s">
@@ -7908,13 +7929,13 @@
     </row>
     <row r="250" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="4" t="s">
@@ -7924,13 +7945,13 @@
     </row>
     <row r="251" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4" t="s">
@@ -7940,13 +7961,13 @@
     </row>
     <row r="252" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="4" t="s">
@@ -7956,13 +7977,13 @@
     </row>
     <row r="253" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="4" t="s">
@@ -7972,13 +7993,13 @@
     </row>
     <row r="254" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="D254" s="4"/>
       <c r="E254" s="4" t="s">
@@ -7986,15 +8007,15 @@
       </c>
       <c r="F254" s="4"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>672</v>
+        <v>691</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>673</v>
+        <v>692</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4" t="s">
@@ -8002,15 +8023,15 @@
       </c>
       <c r="F255" s="4"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="4" t="s">
@@ -8018,15 +8039,15 @@
       </c>
       <c r="F256" s="4"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>678</v>
+        <v>697</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>679</v>
+        <v>698</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="4" t="s">
@@ -8036,13 +8057,13 @@
     </row>
     <row r="258" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>682</v>
+        <v>701</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="4" t="s">
@@ -8051,420 +8072,20 @@
       <c r="F258" s="4"/>
     </row>
     <row r="259" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A259" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="B259" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F259" s="4"/>
-    </row>
-    <row r="260" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A260" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="B260" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F260" s="4"/>
-    </row>
-    <row r="261" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A261" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="B261" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="D261" s="4"/>
-      <c r="E261" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F261" s="4"/>
-    </row>
-    <row r="262" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A262" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="B262" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="D262" s="4"/>
-      <c r="E262" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F262" s="4"/>
-    </row>
-    <row r="263" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A263" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="D263" s="4"/>
-      <c r="E263" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F263" s="4"/>
-    </row>
-    <row r="264" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A264" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B264" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F264" s="4"/>
-    </row>
-    <row r="265" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A265" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="B265" s="4" t="s">
+      <c r="A259" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="B259" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="D265" s="4"/>
-      <c r="E265" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F265" s="4"/>
-    </row>
-    <row r="266" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A266" s="3" t="s">
+      <c r="C259" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="B266" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="D266" s="4"/>
-      <c r="E266" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F266" s="4"/>
-    </row>
-    <row r="267" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A267" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="B267" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="D267" s="4"/>
-      <c r="E267" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F267" s="4"/>
-    </row>
-    <row r="268" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A268" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B268" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="D268" s="4"/>
-      <c r="E268" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F268" s="4"/>
-    </row>
-    <row r="269" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A269" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="B269" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="D269" s="4"/>
-      <c r="E269" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F269" s="4"/>
-    </row>
-    <row r="270" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A270" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="B270" s="4" t="s">
-        <v>717</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="D270" s="4"/>
-      <c r="E270" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F270" s="4"/>
-    </row>
-    <row r="271" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="B271" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="D271" s="4"/>
-      <c r="E271" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F271" s="4"/>
-    </row>
-    <row r="272" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A272" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="B272" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="D272" s="4"/>
-      <c r="E272" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F272" s="4"/>
-    </row>
-    <row r="273" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A273" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="B273" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D273" s="4"/>
-      <c r="E273" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F273" s="4"/>
-    </row>
-    <row r="274" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A274" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="B274" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="D274" s="4"/>
-      <c r="E274" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F274" s="4"/>
-    </row>
-    <row r="275" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A275" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="B275" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="D275" s="4"/>
-      <c r="E275" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F275" s="4"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A276" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="B276" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="C276" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="D276" s="4"/>
-      <c r="E276" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F276" s="4"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A277" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="B277" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="D277" s="4"/>
-      <c r="E277" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F277" s="4"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A278" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="D278" s="4"/>
-      <c r="E278" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F278" s="4"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A279" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="B279" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="D279" s="4"/>
-      <c r="E279" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F279" s="4"/>
-    </row>
-    <row r="280" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A280" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="B280" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D280" s="4"/>
-      <c r="E280" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F280" s="4"/>
-    </row>
-    <row r="281" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A281" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>750</v>
-      </c>
-      <c r="D281" s="4"/>
-      <c r="E281" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F281" s="4"/>
-    </row>
-    <row r="282" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A282" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B282" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="D282" s="4"/>
-      <c r="E282" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F282" s="4"/>
-    </row>
-    <row r="283" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A283" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="B283" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="D283" s="4"/>
-      <c r="E283" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F283" s="4"/>
-    </row>
-    <row r="284" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A284" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="D284" s="6"/>
-      <c r="E284" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F284" s="6"/>
+      <c r="D259" s="6"/>
+      <c r="E259" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F259" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8506,13 +8127,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>760</v>
+        <v>705</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>761</v>
+        <v>706</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>762</v>
+        <v>707</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
@@ -8522,13 +8143,13 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>760</v>
+        <v>705</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>763</v>
+        <v>708</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>764</v>
+        <v>709</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
@@ -8538,13 +8159,13 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>765</v>
+        <v>710</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>766</v>
+        <v>711</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>767</v>
+        <v>712</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
@@ -8554,13 +8175,13 @@
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>765</v>
+        <v>710</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>768</v>
+        <v>713</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>769</v>
+        <v>714</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
@@ -8570,7 +8191,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>770</v>
+        <v>715</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>239</v>
@@ -8584,13 +8205,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>771</v>
+        <v>716</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>572</v>
+        <v>517</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -8598,13 +8219,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>772</v>
+        <v>717</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>773</v>
+        <v>718</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>774</v>
+        <v>719</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -8614,7 +8235,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>775</v>
+        <v>720</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>242</v>
@@ -8628,7 +8249,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>776</v>
+        <v>721</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>245</v>
@@ -8642,7 +8263,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>777</v>
+        <v>722</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>248</v>
@@ -8656,7 +8277,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>778</v>
+        <v>723</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>251</v>
@@ -8670,7 +8291,7 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>779</v>
+        <v>724</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>254</v>
@@ -8684,7 +8305,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>780</v>
+        <v>725</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>257</v>
@@ -8700,7 +8321,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>781</v>
+        <v>726</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>30</v>
@@ -8714,13 +8335,13 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>782</v>
+        <v>727</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>783</v>
+        <v>728</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>784</v>
+        <v>729</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
@@ -8730,7 +8351,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>785</v>
+        <v>730</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>33</v>
@@ -8744,13 +8365,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>786</v>
+        <v>731</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>787</v>
+        <v>732</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>788</v>
+        <v>733</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
@@ -8760,7 +8381,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>789</v>
+        <v>734</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>36</v>
@@ -8774,7 +8395,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>790</v>
+        <v>735</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>39</v>
@@ -8788,13 +8409,13 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>791</v>
+        <v>736</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>792</v>
+        <v>737</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>793</v>
+        <v>738</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -8802,7 +8423,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>794</v>
+        <v>739</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>215</v>
@@ -8816,7 +8437,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>795</v>
+        <v>740</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>42</v>
@@ -8830,13 +8451,13 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>795</v>
+        <v>740</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>796</v>
+        <v>741</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>797</v>
+        <v>742</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
@@ -8846,7 +8467,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>798</v>
+        <v>743</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>264</v>
@@ -8860,13 +8481,13 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>798</v>
+        <v>743</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>799</v>
+        <v>744</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>800</v>
+        <v>745</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
@@ -8876,7 +8497,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>801</v>
+        <v>746</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>267</v>
@@ -8890,13 +8511,13 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>801</v>
+        <v>746</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>802</v>
+        <v>747</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>803</v>
+        <v>748</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
@@ -8906,13 +8527,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>804</v>
+        <v>749</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>805</v>
+        <v>750</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>806</v>
+        <v>751</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
@@ -8922,13 +8543,13 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>804</v>
+        <v>749</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>807</v>
+        <v>752</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>808</v>
+        <v>753</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
@@ -8938,13 +8559,13 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>809</v>
+        <v>754</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>810</v>
+        <v>755</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>811</v>
+        <v>756</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -8952,13 +8573,13 @@
     </row>
     <row r="32" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>809</v>
+        <v>754</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>812</v>
+        <v>757</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>813</v>
+        <v>758</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
@@ -8968,13 +8589,13 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>582</v>
+        <v>527</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>583</v>
+        <v>528</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -8982,13 +8603,13 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>815</v>
+        <v>760</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>816</v>
+        <v>761</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
@@ -8998,7 +8619,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>221</v>
@@ -9012,13 +8633,13 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>819</v>
+        <v>764</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
@@ -9028,7 +8649,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>820</v>
+        <v>765</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>224</v>
@@ -9042,7 +8663,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>821</v>
+        <v>766</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>227</v>
@@ -9056,13 +8677,13 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>821</v>
+        <v>766</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>819</v>
+        <v>764</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
@@ -9072,7 +8693,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>822</v>
+        <v>767</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>230</v>
@@ -9086,7 +8707,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>823</v>
+        <v>768</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>218</v>
@@ -9100,13 +8721,13 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>824</v>
+        <v>769</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>825</v>
+        <v>770</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>826</v>
+        <v>771</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -9114,27 +8735,27 @@
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>824</v>
+        <v>769</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>827</v>
+        <v>772</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>828</v>
+        <v>773</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>829</v>
+        <v>774</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>830</v>
+        <v>775</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>831</v>
+        <v>776</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
@@ -9144,27 +8765,27 @@
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>829</v>
+        <v>774</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>827</v>
+        <v>772</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
-        <v>828</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>832</v>
+        <v>777</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>833</v>
+        <v>778</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>834</v>
+        <v>779</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -9172,27 +8793,27 @@
     </row>
     <row r="47" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>832</v>
+        <v>777</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>827</v>
+        <v>772</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4" t="s">
-        <v>828</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>835</v>
+        <v>780</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>836</v>
+        <v>781</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>837</v>
+        <v>782</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -9200,13 +8821,13 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>835</v>
+        <v>780</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>838</v>
+        <v>783</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>839</v>
+        <v>784</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4" t="s">
@@ -9216,13 +8837,13 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>840</v>
+        <v>785</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>275</v>
+        <v>786</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>276</v>
+        <v>787</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -9230,13 +8851,13 @@
     </row>
     <row r="51" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>840</v>
+        <v>785</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>841</v>
+        <v>788</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>842</v>
+        <v>789</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4" t="s">
@@ -9246,13 +8867,13 @@
     </row>
     <row r="52" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>843</v>
+        <v>790</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>844</v>
+        <v>791</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>845</v>
+        <v>792</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -9260,13 +8881,13 @@
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>843</v>
+        <v>790</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>846</v>
+        <v>793</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>847</v>
+        <v>794</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4" t="s">
@@ -9276,13 +8897,13 @@
     </row>
     <row r="54" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>848</v>
+        <v>795</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>849</v>
+        <v>796</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>850</v>
+        <v>797</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4" t="s">
@@ -9292,13 +8913,13 @@
     </row>
     <row r="55" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>848</v>
+        <v>795</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>851</v>
+        <v>798</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>852</v>
+        <v>799</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
@@ -9313,6 +8934,424 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" ht="63" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" ht="47.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -9349,7 +9388,7 @@
         <v>853</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>606</v>
+        <v>551</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>854</v>
@@ -9409,10 +9448,10 @@
         <v>862</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>351</v>
+        <v>291</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -10089,10 +10128,10 @@
         <v>975</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>543</v>
+        <v>488</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>544</v>
+        <v>489</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -10300,7 +10339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -10674,7 +10713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -11880,7 +11919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
@@ -12013,10 +12052,10 @@
         <v>1190</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
@@ -12029,10 +12068,10 @@
         <v>1190</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -12045,7 +12084,7 @@
         <v>1190</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>827</v>
+        <v>772</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>1191</v>
@@ -12142,7 +12181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
